--- a/storage/app/assessTemplate/normal.xlsx
+++ b/storage/app/assessTemplate/normal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485B6D58-16FB-4E7F-B5D8-FA4842B2CB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F28AE2-C080-413F-96E0-9A2FD075CF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="390" windowWidth="28770" windowHeight="15450" xr2:uid="{E413E3D2-D5C9-4FCA-87F1-38CEB89E0E09}"/>
+    <workbookView xWindow="45" yWindow="765" windowWidth="28755" windowHeight="15435" xr2:uid="{E413E3D2-D5C9-4FCA-87F1-38CEB89E0E09}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（通常）" sheetId="2" r:id="rId1"/>
@@ -260,7 +260,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="#,##0.0;[Red]\-#,##0.0"/>
     <numFmt numFmtId="177" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="178" formatCode="#,##0&quot;千円&quot;"/>
@@ -269,6 +269,7 @@
     <numFmt numFmtId="181" formatCode="0.0%"/>
     <numFmt numFmtId="182" formatCode="#,##0&quot;年&quot;"/>
     <numFmt numFmtId="183" formatCode="0;_ꐀ"/>
+    <numFmt numFmtId="184" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@" x16r2:formatCode16="[$-ja-JP-x-gannen]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -903,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1095,6 +1096,107 @@
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="23" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="40" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="40" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1130,103 +1232,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="23" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="40" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="40" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1549,7 +1556,7 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1" customWidth="1"/>
@@ -1568,68 +1575,68 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
+    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
       <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="65" t="s">
+    <row r="3" spans="1:16" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="71"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="100"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="68"/>
-      <c r="N4" s="72"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="101"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1639,7 +1646,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1656,23 +1663,26 @@
       <c r="L6" s="12"/>
       <c r="N6" s="13"/>
     </row>
-    <row r="7" spans="1:15" ht="29.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="83"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="86"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="90"/>
       <c r="J7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="99"/>
-      <c r="L7" s="100"/>
+      <c r="K7" s="91">
+        <f>K10</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="92"/>
       <c r="M7" s="16"/>
       <c r="N7" s="13"/>
     </row>
-    <row r="8" spans="1:15" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" s="11"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -1684,7 +1694,7 @@
       <c r="L8" s="19"/>
       <c r="N8" s="13"/>
     </row>
-    <row r="9" spans="1:15" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" s="11"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -1696,7 +1706,7 @@
       <c r="L9" s="19"/>
       <c r="N9" s="13"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="95.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1704,11 +1714,11 @@
       <c r="F10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="K10" s="102"/>
       <c r="L10" s="19"/>
       <c r="N10" s="13"/>
     </row>
-    <row r="11" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="11"/>
       <c r="B11" s="20" t="s">
         <v>10</v>
@@ -1721,8 +1731,9 @@
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
       <c r="N11" s="13"/>
-    </row>
-    <row r="12" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="P11" s="64"/>
+    </row>
+    <row r="12" spans="1:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="11"/>
       <c r="B12" s="21"/>
       <c r="E12" s="22"/>
@@ -1732,29 +1743,29 @@
       <c r="M12" s="24"/>
       <c r="N12" s="13"/>
     </row>
-    <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="E13" s="75" t="s">
+      <c r="B13" s="80"/>
+      <c r="C13" s="80"/>
+      <c r="E13" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="78"/>
+      <c r="H13" s="72"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="77" t="s">
+      <c r="J13" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="78"/>
+      <c r="K13" s="72"/>
       <c r="N13" s="13"/>
     </row>
-    <row r="14" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="E14" s="76"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="E14" s="83"/>
       <c r="G14" s="25" t="s">
         <v>14</v>
       </c>
@@ -1770,17 +1781,17 @@
       </c>
       <c r="N14" s="13"/>
     </row>
-    <row r="15" spans="1:15" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A15" s="11"/>
       <c r="B15" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="86" t="s">
+      <c r="D15" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="87"/>
-      <c r="F15" s="86" t="s">
+      <c r="E15" s="78"/>
+      <c r="F15" s="73" t="s">
         <v>19</v>
       </c>
       <c r="G15" s="29"/>
@@ -1790,15 +1801,15 @@
       <c r="K15" s="30"/>
       <c r="N15" s="13"/>
     </row>
-    <row r="16" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="11"/>
       <c r="B16" s="32" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="86"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
       <c r="I16" s="31"/>
@@ -1812,9 +1823,9 @@
         <v>21</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="86"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="73"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
       <c r="I17" s="31"/>
@@ -1832,28 +1843,28 @@
     </row>
     <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73" t="s">
+      <c r="B20" s="80"/>
+      <c r="C20" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="75" t="s">
+      <c r="E20" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="93" t="s">
+      <c r="G20" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="94"/>
-      <c r="J20" s="77" t="s">
+      <c r="H20" s="70"/>
+      <c r="J20" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="78"/>
+      <c r="K20" s="72"/>
       <c r="N20" s="13"/>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="E21" s="76"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="E21" s="83"/>
       <c r="G21" s="37"/>
       <c r="H21" s="26" t="s">
         <v>26</v>
@@ -1870,11 +1881,11 @@
         <v>17</v>
       </c>
       <c r="C22" s="38"/>
-      <c r="D22" s="86" t="s">
+      <c r="D22" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="95"/>
-      <c r="F22" s="86" t="s">
+      <c r="E22" s="74"/>
+      <c r="F22" s="73" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="39"/>
@@ -1890,9 +1901,9 @@
         <v>20</v>
       </c>
       <c r="C23" s="38"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="86"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="73"/>
       <c r="G23" s="42"/>
       <c r="H23" s="43"/>
       <c r="I23" s="41"/>
@@ -1906,9 +1917,9 @@
         <v>21</v>
       </c>
       <c r="C24" s="38"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="86"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="73"/>
       <c r="G24" s="44"/>
       <c r="H24" s="45"/>
       <c r="I24" s="41"/>
@@ -1941,84 +1952,84 @@
       <c r="A27" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="97"/>
-      <c r="L27" s="97"/>
-      <c r="M27" s="97"/>
-      <c r="N27" s="98"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
+      <c r="N27" s="77"/>
       <c r="O27" s="55"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="90"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="90"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="66"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="90"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="66"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="56"/>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="92"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="68"/>
     </row>
     <row r="32" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E32" s="57"/>
@@ -2081,6 +2092,28 @@
     <row r="73" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="B28:N28"/>
     <mergeCell ref="B29:N29"/>
     <mergeCell ref="B30:N30"/>
@@ -2091,28 +2124,6 @@
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
     <mergeCell ref="B27:N27"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">

--- a/storage/app/assessTemplate/normal.xlsx
+++ b/storage/app/assessTemplate/normal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F28AE2-C080-413F-96E0-9A2FD075CF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AC3AAC-BCA1-456D-AEDD-1237FB915761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="765" windowWidth="28755" windowHeight="15435" xr2:uid="{E413E3D2-D5C9-4FCA-87F1-38CEB89E0E09}"/>
+    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{E413E3D2-D5C9-4FCA-87F1-38CEB89E0E09}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（通常）" sheetId="2" r:id="rId1"/>
@@ -1100,21 +1100,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1136,14 +1123,6 @@
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1232,8 +1211,29 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1576,8 +1576,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
       <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1587,47 +1587,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:16" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="97"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="99"/>
-      <c r="K4" s="100"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="95"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="97"/>
-      <c r="N4" s="101"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="96"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1635,8 +1635,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1665,20 +1665,20 @@
     </row>
     <row r="7" spans="1:16" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="86"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="90"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="85"/>
       <c r="J7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="86">
         <f>K10</f>
         <v>0</v>
       </c>
-      <c r="L7" s="92"/>
+      <c r="L7" s="87"/>
       <c r="M7" s="16"/>
       <c r="N7" s="13"/>
     </row>
@@ -1714,7 +1714,7 @@
       <c r="F10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="K10" s="102"/>
+      <c r="K10" s="65"/>
       <c r="L10" s="19"/>
       <c r="N10" s="13"/>
     </row>
@@ -1745,27 +1745,27 @@
     </row>
     <row r="13" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
-      <c r="E13" s="82" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="E13" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="71" t="s">
+      <c r="G13" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="72"/>
+      <c r="H13" s="69"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="71" t="s">
+      <c r="J13" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="72"/>
+      <c r="K13" s="69"/>
       <c r="N13" s="13"/>
     </row>
     <row r="14" spans="1:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
-      <c r="B14" s="81"/>
-      <c r="C14" s="81"/>
-      <c r="E14" s="83"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="E14" s="78"/>
       <c r="G14" s="25" t="s">
         <v>14</v>
       </c>
@@ -1787,11 +1787,11 @@
         <v>17</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="78"/>
-      <c r="F15" s="73" t="s">
+      <c r="E15" s="73"/>
+      <c r="F15" s="70" t="s">
         <v>19</v>
       </c>
       <c r="G15" s="29"/>
@@ -1807,9 +1807,9 @@
         <v>20</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="73"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
       <c r="I16" s="31"/>
@@ -1823,9 +1823,9 @@
         <v>21</v>
       </c>
       <c r="C17" s="28"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="73"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="70"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
       <c r="I17" s="31"/>
@@ -1843,28 +1843,28 @@
     </row>
     <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80" t="s">
+      <c r="B20" s="75"/>
+      <c r="C20" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="70"/>
-      <c r="J20" s="71" t="s">
+      <c r="H20" s="67"/>
+      <c r="J20" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="72"/>
+      <c r="K20" s="69"/>
       <c r="N20" s="13"/>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81"/>
-      <c r="E21" s="83"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="E21" s="78"/>
       <c r="G21" s="37"/>
       <c r="H21" s="26" t="s">
         <v>26</v>
@@ -1881,11 +1881,11 @@
         <v>17</v>
       </c>
       <c r="C22" s="38"/>
-      <c r="D22" s="73" t="s">
+      <c r="D22" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="74"/>
-      <c r="F22" s="73" t="s">
+      <c r="E22" s="71"/>
+      <c r="F22" s="70" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="39"/>
@@ -1901,9 +1901,9 @@
         <v>20</v>
       </c>
       <c r="C23" s="38"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="73"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="70"/>
       <c r="G23" s="42"/>
       <c r="H23" s="43"/>
       <c r="I23" s="41"/>
@@ -1917,9 +1917,9 @@
         <v>21</v>
       </c>
       <c r="C24" s="38"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="73"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="70"/>
       <c r="G24" s="44"/>
       <c r="H24" s="45"/>
       <c r="I24" s="41"/>
@@ -1952,84 +1952,84 @@
       <c r="A27" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="77"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="98"/>
       <c r="O27" s="55"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="99"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="100"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="66"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="99"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="99"/>
+      <c r="M29" s="99"/>
+      <c r="N29" s="100"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="66"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="99"/>
+      <c r="N30" s="100"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="56"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="68"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="102"/>
     </row>
     <row r="32" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E32" s="57"/>
@@ -2091,7 +2091,7 @@
     <row r="67" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="73" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="28">
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="B4:D4"/>
@@ -2108,22 +2108,18 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="B27:N31"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="B27:N27"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
